--- a/BAL/compiled_data.xlsx
+++ b/BAL/compiled_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q95"/>
+  <dimension ref="A1:Z95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,51 @@
           <t>M</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>V_nominal</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>prop_speed_hz</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>test_block</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>advance_ratio_J</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>advance_ratio_nominal_J</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>rho_est_kg_m3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Ct_formula_input</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>thrust_single_prop_N</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>thrust_total_2props_N</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -569,6 +614,29 @@
       <c r="Q2" t="n">
         <v>0.118</v>
       </c>
+      <c r="R2" t="n">
+        <v>40</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0.9437771426143591</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.143668</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -624,6 +692,29 @@
       <c r="Q3" t="n">
         <v>0.118</v>
       </c>
+      <c r="R3" t="n">
+        <v>40</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0.9461677064777406</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.08928999999999999</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,6 +770,29 @@
       <c r="Q4" t="n">
         <v>0.118</v>
       </c>
+      <c r="R4" t="n">
+        <v>40</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0.9509586855101589</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.0238</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -734,6 +848,29 @@
       <c r="Q5" t="n">
         <v>0.118</v>
       </c>
+      <c r="R5" t="n">
+        <v>40</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0.9485573270176487</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.006009</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -789,6 +926,29 @@
       <c r="Q6" t="n">
         <v>0.118</v>
       </c>
+      <c r="R6" t="n">
+        <v>40</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0.9468154756064965</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.004415</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -844,6 +1004,35 @@
       <c r="Q7" t="n">
         <v>0.118</v>
       </c>
+      <c r="R7" t="n">
+        <v>40</v>
+      </c>
+      <c r="S7" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>5.022432950957273</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.942545081772415</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.068538</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.1709703563491698</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.3419407126983397</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -899,6 +1088,35 @@
       <c r="Q8" t="n">
         <v>0.118</v>
       </c>
+      <c r="R8" t="n">
+        <v>40</v>
+      </c>
+      <c r="S8" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>5.021183900235822</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.9421451824264911</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.069753</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.1739273903384269</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.3478547806768539</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -954,6 +1172,35 @@
       <c r="Q9" t="n">
         <v>0.118</v>
       </c>
+      <c r="R9" t="n">
+        <v>40</v>
+      </c>
+      <c r="S9" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>5.011191494464208</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.9389464683929988</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.039497</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.09815042870685259</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.1963008574137052</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1009,6 +1256,35 @@
       <c r="Q10" t="n">
         <v>0.118</v>
       </c>
+      <c r="R10" t="n">
+        <v>40</v>
+      </c>
+      <c r="S10" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>5.019934849514369</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.9414750681786036</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.021857</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.05446112822824693</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.1089222564564939</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1064,6 +1340,35 @@
       <c r="Q11" t="n">
         <v>0.118</v>
       </c>
+      <c r="R11" t="n">
+        <v>40</v>
+      </c>
+      <c r="S11" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>5.022432950957273</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.9420044766208393</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.069106</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.1722883772892474</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.3445767545784948</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1119,6 +1424,35 @@
       <c r="Q12" t="n">
         <v>0.118</v>
       </c>
+      <c r="R12" t="n">
+        <v>40</v>
+      </c>
+      <c r="S12" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>3.589572288037498</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.572602426511568</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.9412048399730413</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.06592000000000001</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3211436674033942</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.6422873348067885</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1174,6 +1508,35 @@
       <c r="Q13" t="n">
         <v>0.118</v>
       </c>
+      <c r="R13" t="n">
+        <v>40</v>
+      </c>
+      <c r="S13" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>3.590465438644126</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.572602426511568</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.9413343862281897</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.067001</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.3264549215004066</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.6529098430008131</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1229,6 +1592,35 @@
       <c r="Q14" t="n">
         <v>0.118</v>
       </c>
+      <c r="R14" t="n">
+        <v>40</v>
+      </c>
+      <c r="S14" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>3.590465438644126</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.572602426511568</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.9407938554293219</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.036637</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1784072047772376</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3568144095544752</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1284,6 +1676,35 @@
       <c r="Q15" t="n">
         <v>0.118</v>
       </c>
+      <c r="R15" t="n">
+        <v>40</v>
+      </c>
+      <c r="S15" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>3.586892836217614</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.572602426511568</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.9394652522183414</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.024917</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.1211642465235651</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.2423284930471303</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1339,6 +1760,35 @@
       <c r="Q16" t="n">
         <v>0.118</v>
       </c>
+      <c r="R16" t="n">
+        <v>40</v>
+      </c>
+      <c r="S16" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>3.593144890464009</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.572602426511568</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.9419930359095053</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.075408</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.3676741750452225</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.7353483500904451</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1394,6 +1844,35 @@
       <c r="Q17" t="n">
         <v>0.118</v>
       </c>
+      <c r="R17" t="n">
+        <v>40</v>
+      </c>
+      <c r="S17" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>2.515032666659997</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.9418636354619838</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.099118</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.985790977485384</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-1.971581954970768</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1449,6 +1928,35 @@
       <c r="Q18" t="n">
         <v>0.118</v>
       </c>
+      <c r="R18" t="n">
+        <v>40</v>
+      </c>
+      <c r="S18" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>2.515657985572642</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.9419930359095053</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.042608</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.4238216328562167</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.8476432657124334</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1504,6 +2012,35 @@
       <c r="Q19" t="n">
         <v>0.118</v>
       </c>
+      <c r="R19" t="n">
+        <v>40</v>
+      </c>
+      <c r="S19" t="n">
+        <v>123</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>MANDATORY</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>1.60761154855643</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.60040970488445</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.939994468696065</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.137869</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-3.342696609973962</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-6.685393219947923</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1559,6 +2096,35 @@
       <c r="Q20" t="n">
         <v>0.118</v>
       </c>
+      <c r="R20" t="n">
+        <v>40</v>
+      </c>
+      <c r="S20" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>2.515032666659997</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.9413229559927174</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.023485</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.2334390427240548</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.4668780854481096</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1614,6 +2180,35 @@
       <c r="Q21" t="n">
         <v>0.118</v>
       </c>
+      <c r="R21" t="n">
+        <v>40</v>
+      </c>
+      <c r="S21" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>2.522536493611742</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.945307915677594</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.052693</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5259815359001723</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.051963071800345</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1669,6 +2264,35 @@
       <c r="Q22" t="n">
         <v>0.118</v>
       </c>
+      <c r="R22" t="n">
+        <v>40</v>
+      </c>
+      <c r="S22" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>2.514407347747351</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.9403826611661118</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.050307</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.4995481001056624</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.9990962002113248</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1724,6 +2348,29 @@
       <c r="Q23" t="n">
         <v>0.059</v>
       </c>
+      <c r="R23" t="n">
+        <v>20</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>0.9429449944005165</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.130139</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1779,6 +2426,29 @@
       <c r="Q24" t="n">
         <v>0.059</v>
       </c>
+      <c r="R24" t="n">
+        <v>20</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>0.9450857536973202</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.070239</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1834,6 +2504,29 @@
       <c r="Q25" t="n">
         <v>0.059</v>
       </c>
+      <c r="R25" t="n">
+        <v>20</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>0.9466860437733201</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.005755</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1889,6 +2582,29 @@
       <c r="Q26" t="n">
         <v>0.059</v>
       </c>
+      <c r="R26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>0.9440263533390492</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.021631</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1944,6 +2660,29 @@
       <c r="Q27" t="n">
         <v>0.059</v>
       </c>
+      <c r="R27" t="n">
+        <v>20</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>0.9450857536973202</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.019315</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1999,6 +2738,35 @@
       <c r="Q28" t="n">
         <v>0.059</v>
       </c>
+      <c r="R28" t="n">
+        <v>20</v>
+      </c>
+      <c r="S28" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>3.583960972269771</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.9432262440242266</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.073271</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.08975547989868962</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.1795109597973792</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2054,6 +2822,35 @@
       <c r="Q29" t="n">
         <v>0.059</v>
       </c>
+      <c r="R29" t="n">
+        <v>20</v>
+      </c>
+      <c r="S29" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>3.583960972269771</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.9432262440242266</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.074086</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.09075383826854168</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.1815076765370834</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2109,6 +2906,35 @@
       <c r="Q30" t="n">
         <v>0.059</v>
       </c>
+      <c r="R30" t="n">
+        <v>20</v>
+      </c>
+      <c r="S30" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>3.582177907109438</v>
+      </c>
+      <c r="V30" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.9429665696318674</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.045825</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.0561192358062397</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.1122384716124794</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2164,6 +2990,35 @@
       <c r="Q31" t="n">
         <v>0.059</v>
       </c>
+      <c r="R31" t="n">
+        <v>20</v>
+      </c>
+      <c r="S31" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>3.578611776788771</v>
+      </c>
+      <c r="V31" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.9419064022629223</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-0.015115</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-0.018489658033754</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-0.036979316067508</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2219,6 +3074,35 @@
       <c r="Q32" t="n">
         <v>0.059</v>
       </c>
+      <c r="R32" t="n">
+        <v>20</v>
+      </c>
+      <c r="S32" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>3.587527102590437</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.9453673434166866</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-0.067943</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-0.0834177158334319</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.1668354316668638</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2274,6 +3158,35 @@
       <c r="Q33" t="n">
         <v>0.118</v>
       </c>
+      <c r="R33" t="n">
+        <v>40</v>
+      </c>
+      <c r="S33" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>REPLICATE</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>2.512531391009415</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.9416156146610482</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-0.042555</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-0.4231248438412001</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-0.8462496876824002</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2329,6 +3242,35 @@
       <c r="Q34" t="n">
         <v>0.118</v>
       </c>
+      <c r="R34" t="n">
+        <v>40</v>
+      </c>
+      <c r="S34" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>5.017436748071466</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.9420261793570343</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.069578</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.1734691183582324</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.3469382367164649</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2384,6 +3326,35 @@
       <c r="Q35" t="n">
         <v>0.118</v>
       </c>
+      <c r="R35" t="n">
+        <v>40</v>
+      </c>
+      <c r="S35" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>5.018685798792918</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.9416156146610482</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.069299</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.1726982264427296</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.3453964528854592</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2439,6 +3410,35 @@
       <c r="Q36" t="n">
         <v>0.118</v>
       </c>
+      <c r="R36" t="n">
+        <v>40</v>
+      </c>
+      <c r="S36" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>5.019934849514369</v>
+      </c>
+      <c r="V36" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.9414750681786036</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.036416</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.09073781605709108</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.1814756321141822</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2494,6 +3494,35 @@
       <c r="Q37" t="n">
         <v>0.118</v>
       </c>
+      <c r="R37" t="n">
+        <v>40</v>
+      </c>
+      <c r="S37" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>5.021183900235822</v>
+      </c>
+      <c r="V37" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.9416046516276234</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-0.026972</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-0.06721543357482579</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-0.1344308671496516</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2549,6 +3578,35 @@
       <c r="Q38" t="n">
         <v>0.118</v>
       </c>
+      <c r="R38" t="n">
+        <v>40</v>
+      </c>
+      <c r="S38" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>5.022432950957273</v>
+      </c>
+      <c r="V38" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.9420044766208393</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-0.07820199999999999</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-0.1949656423577363</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-0.3899312847154726</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2604,6 +3662,35 @@
       <c r="Q39" t="n">
         <v>0.118</v>
       </c>
+      <c r="R39" t="n">
+        <v>40</v>
+      </c>
+      <c r="S39" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>3.591358589250754</v>
+      </c>
+      <c r="V39" t="n">
+        <v>3.572602426511568</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.9414638714692634</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.066825</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.3256421686170374</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.6512843372340749</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2659,6 +3746,35 @@
       <c r="Q40" t="n">
         <v>0.118</v>
       </c>
+      <c r="R40" t="n">
+        <v>40</v>
+      </c>
+      <c r="S40" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>3.589572288037498</v>
+      </c>
+      <c r="V40" t="n">
+        <v>3.572602426511568</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.9401239271507927</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.06642199999999999</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.323217648641256</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.6464352972825119</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2714,6 +3830,35 @@
       <c r="Q41" t="n">
         <v>0.118</v>
       </c>
+      <c r="R41" t="n">
+        <v>40</v>
+      </c>
+      <c r="S41" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>3.595824342283893</v>
+      </c>
+      <c r="V41" t="n">
+        <v>3.572602426511568</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.9426513599413739</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.033686</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.1643609167230718</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.3287218334461435</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2769,6 +3914,35 @@
       <c r="Q42" t="n">
         <v>0.118</v>
       </c>
+      <c r="R42" t="n">
+        <v>40</v>
+      </c>
+      <c r="S42" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>3.593144890464009</v>
+      </c>
+      <c r="V42" t="n">
+        <v>3.572602426511568</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.9414522821575482</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-0.03007</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-0.1465310807509843</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-0.2930621615019687</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2824,6 +3998,35 @@
       <c r="Q43" t="n">
         <v>0.118</v>
       </c>
+      <c r="R43" t="n">
+        <v>40</v>
+      </c>
+      <c r="S43" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>3.587785986824243</v>
+      </c>
+      <c r="V43" t="n">
+        <v>3.572602426511568</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.9395947954699641</v>
+      </c>
+      <c r="X43" t="n">
+        <v>-0.084686</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-0.4118605876692315</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-0.823721175338463</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2879,6 +4082,35 @@
       <c r="Q44" t="n">
         <v>0.118</v>
       </c>
+      <c r="R44" t="n">
+        <v>40</v>
+      </c>
+      <c r="S44" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>2.516283304485288</v>
+      </c>
+      <c r="V44" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.9418519614188557</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.051672</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.5139042356987421</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.027808471397484</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2934,6 +4166,35 @@
       <c r="Q45" t="n">
         <v>0.118</v>
       </c>
+      <c r="R45" t="n">
+        <v>40</v>
+      </c>
+      <c r="S45" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>2.515657985572642</v>
+      </c>
+      <c r="V45" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.9409115284055909</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.051737</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.5140369181545068</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.028073836309014</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2989,6 +4250,35 @@
       <c r="Q46" t="n">
         <v>0.118</v>
       </c>
+      <c r="R46" t="n">
+        <v>40</v>
+      </c>
+      <c r="S46" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>2.514407347747351</v>
+      </c>
+      <c r="V46" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.9401123585903239</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.018894</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.1875633375501705</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.375126675100341</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3044,6 +4334,35 @@
       <c r="Q47" t="n">
         <v>0.118</v>
       </c>
+      <c r="R47" t="n">
+        <v>40</v>
+      </c>
+      <c r="S47" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>2.510655434271478</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.9379852516423424</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-0.04849</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>-0.4802777563267421</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-0.9605555126534843</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3099,6 +4418,35 @@
       <c r="Q48" t="n">
         <v>0.118</v>
       </c>
+      <c r="R48" t="n">
+        <v>40</v>
+      </c>
+      <c r="S48" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>ZERO</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>2.515032666659997</v>
+      </c>
+      <c r="V48" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.940782276523451</v>
+      </c>
+      <c r="X48" t="n">
+        <v>-0.10897</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>-1.082531037996537</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-2.165062075993074</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3154,6 +4502,29 @@
       <c r="Q49" t="n">
         <v>0.118</v>
       </c>
+      <c r="R49" t="n">
+        <v>40</v>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="n">
+        <v>0.9414403007019765</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.005123</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3209,6 +4580,29 @@
       <c r="Q50" t="n">
         <v>0.118</v>
       </c>
+      <c r="R50" t="n">
+        <v>40</v>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="n">
+        <v>0.9399712573195516</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.004654</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3264,6 +4658,29 @@
       <c r="Q51" t="n">
         <v>0.118</v>
       </c>
+      <c r="R51" t="n">
+        <v>40</v>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="n">
+        <v>0.9397009175849184</v>
+      </c>
+      <c r="X51" t="n">
+        <v>-0.028538</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3319,6 +4736,29 @@
       <c r="Q52" t="n">
         <v>0.118</v>
       </c>
+      <c r="R52" t="n">
+        <v>40</v>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="n">
+        <v>0.939043014328544</v>
+      </c>
+      <c r="X52" t="n">
+        <v>-0.095287</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3374,6 +4814,29 @@
       <c r="Q53" t="n">
         <v>0.118</v>
       </c>
+      <c r="R53" t="n">
+        <v>40</v>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="n">
+        <v>0.9402415970541848</v>
+      </c>
+      <c r="X53" t="n">
+        <v>-0.15327</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3429,6 +4892,29 @@
       <c r="Q54" t="n">
         <v>0.059</v>
       </c>
+      <c r="R54" t="n">
+        <v>20</v>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="n">
+        <v>0.9426632034183552</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.019691</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3484,6 +4970,29 @@
       <c r="Q55" t="n">
         <v>0.059</v>
       </c>
+      <c r="R55" t="n">
+        <v>20</v>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="n">
+        <v>0.9416046516276234</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.019525</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3539,6 +5048,29 @@
       <c r="Q56" t="n">
         <v>0.059</v>
       </c>
+      <c r="R56" t="n">
+        <v>20</v>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="n">
+        <v>0.9456034982687194</v>
+      </c>
+      <c r="X56" t="n">
+        <v>-0.011087</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3594,6 +5126,29 @@
       <c r="Q57" t="n">
         <v>0.059</v>
       </c>
+      <c r="R57" t="n">
+        <v>20</v>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="n">
+        <v>0.9410859513308515</v>
+      </c>
+      <c r="X57" t="n">
+        <v>-0.077986</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3649,6 +5204,29 @@
       <c r="Q58" t="n">
         <v>0.059</v>
       </c>
+      <c r="R58" t="n">
+        <v>20</v>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="n">
+        <v>0.9418858056552121</v>
+      </c>
+      <c r="X58" t="n">
+        <v>-0.139884</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3704,6 +5282,35 @@
       <c r="Q59" t="n">
         <v>0.059</v>
       </c>
+      <c r="R59" t="n">
+        <v>20</v>
+      </c>
+      <c r="S59" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>3.585744037430104</v>
+      </c>
+      <c r="V59" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.9434856738697828</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0.073494</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.09005341229598227</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.1801068245919645</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3759,6 +5366,35 @@
       <c r="Q60" t="n">
         <v>0.059</v>
       </c>
+      <c r="R60" t="n">
+        <v>20</v>
+      </c>
+      <c r="S60" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>3.583960972269771</v>
+      </c>
+      <c r="V60" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.9426857132253589</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0.073171</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.08958161633350274</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.1791632326670055</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3814,6 +5450,35 @@
       <c r="Q61" t="n">
         <v>0.059</v>
       </c>
+      <c r="R61" t="n">
+        <v>20</v>
+      </c>
+      <c r="S61" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>3.591093232911104</v>
+      </c>
+      <c r="V61" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.9458858725393078</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0.042456</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.05215438063115899</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.104308761262318</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3869,6 +5534,35 @@
       <c r="Q62" t="n">
         <v>0.059</v>
       </c>
+      <c r="R62" t="n">
+        <v>20</v>
+      </c>
+      <c r="S62" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
+        <v>3.596442428392103</v>
+      </c>
+      <c r="V62" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0.947744974182635</v>
+      </c>
+      <c r="X62" t="n">
+        <v>-0.021196</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-0.02608905687198815</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-0.0521781137439763</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3924,6 +5618,35 @@
       <c r="Q63" t="n">
         <v>0.059</v>
       </c>
+      <c r="R63" t="n">
+        <v>20</v>
+      </c>
+      <c r="S63" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
+        <v>3.587527102590437</v>
+      </c>
+      <c r="V63" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0.9448265154170203</v>
+      </c>
+      <c r="X63" t="n">
+        <v>-0.077961</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>-0.09566265994171071</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-0.1913253198834214</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3979,6 +5702,35 @@
       <c r="Q64" t="n">
         <v>0.118</v>
       </c>
+      <c r="R64" t="n">
+        <v>40</v>
+      </c>
+      <c r="S64" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>REPLICATE</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
+        <v>2.515032666659997</v>
+      </c>
+      <c r="V64" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.9429449944005165</v>
+      </c>
+      <c r="X64" t="n">
+        <v>-0.047881</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-0.4767534568264832</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.9535069136529664</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4034,6 +5786,35 @@
       <c r="Q65" t="n">
         <v>0.118</v>
       </c>
+      <c r="R65" t="n">
+        <v>40</v>
+      </c>
+      <c r="S65" t="n">
+        <v>123</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>MANDATORY</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
+        <v>1.609211958261315</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.60040970488445</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.9421339751966169</v>
+      </c>
+      <c r="X65" t="n">
+        <v>-0.143137</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>-3.478320637650655</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-6.956641275301309</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4089,6 +5870,35 @@
       <c r="Q66" t="n">
         <v>0.118</v>
       </c>
+      <c r="R66" t="n">
+        <v>40</v>
+      </c>
+      <c r="S66" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
+        <v>5.024931052400176</v>
+      </c>
+      <c r="V66" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0.942263412785484</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0.066972</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0.167013991275895</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.33402798255179</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4144,6 +5954,35 @@
       <c r="Q67" t="n">
         <v>0.118</v>
       </c>
+      <c r="R67" t="n">
+        <v>40</v>
+      </c>
+      <c r="S67" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>5.021183900235822</v>
+      </c>
+      <c r="V67" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.9407938554293219</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.06736</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0.1677195964745696</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.3354391929491393</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4199,6 +6038,35 @@
       <c r="Q68" t="n">
         <v>0.118</v>
       </c>
+      <c r="R68" t="n">
+        <v>40</v>
+      </c>
+      <c r="S68" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>5.016187697350015</v>
+      </c>
+      <c r="V68" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.938925019180838</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0.035831</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0.08903834906143253</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.1780766981228651</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4254,6 +6122,35 @@
       <c r="Q69" t="n">
         <v>0.118</v>
       </c>
+      <c r="R69" t="n">
+        <v>40</v>
+      </c>
+      <c r="S69" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>5.013689595907111</v>
+      </c>
+      <c r="V69" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.9381258146391606</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-0.026894</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>-0.06677343919781815</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.1335468783956363</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4309,6 +6206,35 @@
       <c r="Q70" t="n">
         <v>0.118</v>
       </c>
+      <c r="R70" t="n">
+        <v>40</v>
+      </c>
+      <c r="S70" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>5.024931052400176</v>
+      </c>
+      <c r="V70" t="n">
+        <v>4.996202885806787</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.9417226590335267</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-0.07611900000000001</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>-0.1897157349071025</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-0.3794314698142051</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4364,6 +6290,35 @@
       <c r="Q71" t="n">
         <v>0.118</v>
       </c>
+      <c r="R71" t="n">
+        <v>40</v>
+      </c>
+      <c r="S71" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>2.518159261223224</v>
+      </c>
+      <c r="V71" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.9422395033602101</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.04892</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0.4867343937951902</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.9734687875903805</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4419,6 +6374,35 @@
       <c r="Q72" t="n">
         <v>0.118</v>
       </c>
+      <c r="R72" t="n">
+        <v>40</v>
+      </c>
+      <c r="S72" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>2.515657985572642</v>
+      </c>
+      <c r="V72" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.9403707746536337</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0.049715</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0.4936633049064381</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.9873266098128761</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4474,6 +6458,35 @@
       <c r="Q73" t="n">
         <v>0.118</v>
       </c>
+      <c r="R73" t="n">
+        <v>40</v>
+      </c>
+      <c r="S73" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>2.514407347747351</v>
+      </c>
+      <c r="V73" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.9398420560145361</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.018113</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0.1797585437731535</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.3595170875463071</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4529,6 +6542,35 @@
       <c r="Q74" t="n">
         <v>0.118</v>
       </c>
+      <c r="R74" t="n">
+        <v>40</v>
+      </c>
+      <c r="S74" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>2.512531391009415</v>
+      </c>
+      <c r="V74" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.9386435137252457</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-0.047915</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>-0.4749156213914403</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>-0.9498312427828807</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4584,6 +6626,35 @@
       <c r="Q75" t="n">
         <v>0.118</v>
       </c>
+      <c r="R75" t="n">
+        <v>40</v>
+      </c>
+      <c r="S75" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
+        <v>2.511280753184124</v>
+      </c>
+      <c r="V75" t="n">
+        <v>2.501275650581797</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9383847861433346</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.105967</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.05001590252463</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-2.100031805049261</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4639,6 +6710,35 @@
       <c r="Q76" t="n">
         <v>0.059</v>
       </c>
+      <c r="R76" t="n">
+        <v>20</v>
+      </c>
+      <c r="S76" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>3.585744037430104</v>
+      </c>
+      <c r="V76" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0.9424043149312502</v>
+      </c>
+      <c r="X76" t="n">
+        <v>-0.07494099999999999</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>-0.09172120009041924</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>-0.1834424001808385</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4694,6 +6794,35 @@
       <c r="Q77" t="n">
         <v>0.059</v>
       </c>
+      <c r="R77" t="n">
+        <v>20</v>
+      </c>
+      <c r="S77" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>3.585744037430104</v>
+      </c>
+      <c r="V77" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0.9424043149312502</v>
+      </c>
+      <c r="X77" t="n">
+        <v>-0.020153</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>-0.02466550146678346</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>-0.04933100293356692</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4749,6 +6878,35 @@
       <c r="Q78" t="n">
         <v>0.059</v>
       </c>
+      <c r="R78" t="n">
+        <v>20</v>
+      </c>
+      <c r="S78" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
+        <v>3.58931016775077</v>
+      </c>
+      <c r="V78" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0.9440038009168996</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0.043494</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0.05332318373208658</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0.1066463674641732</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4804,6 +6962,35 @@
       <c r="Q79" t="n">
         <v>0.059</v>
       </c>
+      <c r="R79" t="n">
+        <v>20</v>
+      </c>
+      <c r="S79" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
+        <v>3.591093232911104</v>
+      </c>
+      <c r="V79" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0.9453447478982671</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0.07201</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0.0884089037009123</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.1768178074018246</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4859,6 +7046,35 @@
       <c r="Q80" t="n">
         <v>0.059</v>
       </c>
+      <c r="R80" t="n">
+        <v>20</v>
+      </c>
+      <c r="S80" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
+        <v>3.59465936323177</v>
+      </c>
+      <c r="V80" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0.9464034257814733</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0.070129</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0.08619596346557477</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.1723919269311495</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4914,6 +7130,35 @@
       <c r="Q81" t="n">
         <v>0.059</v>
       </c>
+      <c r="R81" t="n">
+        <v>20</v>
+      </c>
+      <c r="S81" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
+        <v>3.592876298071436</v>
+      </c>
+      <c r="V81" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0.9461447710210198</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0.016533</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0.02031525312102275</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.0406305062420455</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4969,6 +7214,35 @@
       <c r="Q82" t="n">
         <v>0.059</v>
       </c>
+      <c r="R82" t="n">
+        <v>20</v>
+      </c>
+      <c r="S82" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
+        <v>3.591093232911104</v>
+      </c>
+      <c r="V82" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0.9453447478982671</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0.017178</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0.02108996177995099</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0.04217992355990199</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5024,6 +7298,35 @@
       <c r="Q83" t="n">
         <v>0.059</v>
       </c>
+      <c r="R83" t="n">
+        <v>20</v>
+      </c>
+      <c r="S83" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
+        <v>3.576828711628437</v>
+      </c>
+      <c r="V83" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.9394864031074284</v>
+      </c>
+      <c r="X83" t="n">
+        <v>-0.013491</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>-0.01646067422910183</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>-0.03292134845820366</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5079,6 +7382,35 @@
       <c r="Q84" t="n">
         <v>0.059</v>
       </c>
+      <c r="R84" t="n">
+        <v>20</v>
+      </c>
+      <c r="S84" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
+        <v>3.583960972269771</v>
+      </c>
+      <c r="V84" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.9426857132253589</v>
+      </c>
+      <c r="X84" t="n">
+        <v>-0.07795199999999999</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>-0.09543488754327814</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>-0.1908697750865563</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5134,6 +7466,35 @@
       <c r="Q85" t="n">
         <v>0.059</v>
       </c>
+      <c r="R85" t="n">
+        <v>20</v>
+      </c>
+      <c r="S85" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U85" t="n">
+        <v>3.575045646468105</v>
+      </c>
+      <c r="V85" t="n">
+        <v>3.566130320666439</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0.939226494895182</v>
+      </c>
+      <c r="X85" t="n">
+        <v>-0.138428</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>-0.168852407839176</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>-0.337704815678352</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5189,6 +7550,35 @@
       <c r="Q86" t="n">
         <v>0.059</v>
       </c>
+      <c r="R86" t="n">
+        <v>20</v>
+      </c>
+      <c r="S86" t="n">
+        <v>22</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U86" t="n">
+        <v>4.487294201861131</v>
+      </c>
+      <c r="V86" t="n">
+        <v>4.473872584108805</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0.9405662725362874</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0.071614</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0.05558114759230066</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0.1111622951846013</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5244,6 +7634,35 @@
       <c r="Q87" t="n">
         <v>0.059</v>
       </c>
+      <c r="R87" t="n">
+        <v>20</v>
+      </c>
+      <c r="S87" t="n">
+        <v>22</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U87" t="n">
+        <v>4.49624194702935</v>
+      </c>
+      <c r="V87" t="n">
+        <v>4.473872584108805</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0.9437667748230945</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0.07248599999999999</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0.05644935640848711</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0.1128987128169742</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5299,6 +7718,35 @@
       <c r="Q88" t="n">
         <v>0.059</v>
       </c>
+      <c r="R88" t="n">
+        <v>20</v>
+      </c>
+      <c r="S88" t="n">
+        <v>22</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U88" t="n">
+        <v>4.49624194702935</v>
+      </c>
+      <c r="V88" t="n">
+        <v>4.473872584108805</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0.9437667748230945</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0.042851</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0.03337073878349035</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0.06674147756698069</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5354,6 +7802,35 @@
       <c r="Q89" t="n">
         <v>0.059</v>
       </c>
+      <c r="R89" t="n">
+        <v>20</v>
+      </c>
+      <c r="S89" t="n">
+        <v>22</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U89" t="n">
+        <v>4.498478883321403</v>
+      </c>
+      <c r="V89" t="n">
+        <v>4.473872584108805</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0.9445670328083156</v>
+      </c>
+      <c r="X89" t="n">
+        <v>-0.019669</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>-0.0153304619024701</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>-0.0306609238049402</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5409,6 +7886,35 @@
       <c r="Q90" t="n">
         <v>0.059</v>
       </c>
+      <c r="R90" t="n">
+        <v>20</v>
+      </c>
+      <c r="S90" t="n">
+        <v>22</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="U90" t="n">
+        <v>4.494005010737294</v>
+      </c>
+      <c r="V90" t="n">
+        <v>4.473872584108805</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0.9435069516201952</v>
+      </c>
+      <c r="X90" t="n">
+        <v>-0.07237</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>-0.05634350410435955</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>-0.1126870082087191</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5464,6 +7970,29 @@
       <c r="Q91" t="n">
         <v>0.118</v>
       </c>
+      <c r="R91" t="n">
+        <v>40</v>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="n">
+        <v>0.9429449944005165</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0.06848600000000001</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5519,6 +8048,29 @@
       <c r="Q92" t="n">
         <v>0.118</v>
       </c>
+      <c r="R92" t="n">
+        <v>40</v>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="n">
+        <v>0.9413343862281897</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0.068934</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5574,6 +8126,29 @@
       <c r="Q93" t="n">
         <v>0.118</v>
       </c>
+      <c r="R93" t="n">
+        <v>40</v>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="n">
+        <v>0.9427925562330051</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0.037495</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5629,6 +8204,29 @@
       <c r="Q94" t="n">
         <v>0.118</v>
       </c>
+      <c r="R94" t="n">
+        <v>40</v>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="n">
+        <v>0.9419930359095053</v>
+      </c>
+      <c r="X94" t="n">
+        <v>-0.025146</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5683,6 +8281,29 @@
       </c>
       <c r="Q95" t="n">
         <v>0.118</v>
+      </c>
+      <c r="R95" t="n">
+        <v>40</v>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="n">
+        <v>0.9402646596902289</v>
+      </c>
+      <c r="X95" t="n">
+        <v>-0.072852</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
